--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N98_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N98_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.81152061027765</v>
+        <v>6.144372099170118</v>
       </c>
       <c r="D2" t="n">
-        <v>38.3573053211115</v>
+        <v>6.23306211468062</v>
       </c>
       <c r="E2" t="n">
-        <v>7.583333717179077</v>
+        <v>1.2322917290416</v>
       </c>
       <c r="F2" t="n">
-        <v>7.484792714670032</v>
+        <v>1.21627881613388</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.49199297381814</v>
+        <v>6.904948858245448</v>
       </c>
       <c r="D3" t="n">
-        <v>42.46667071441406</v>
+        <v>6.900833991092286</v>
       </c>
       <c r="E3" t="n">
-        <v>7.583333717179077</v>
+        <v>1.2322917290416</v>
       </c>
       <c r="F3" t="n">
-        <v>7.484792714670032</v>
+        <v>1.21627881613388</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>58.16913357468453</v>
+        <v>9.452484205886236</v>
       </c>
       <c r="D4" t="n">
-        <v>58.27249546574873</v>
+        <v>9.46928051318417</v>
       </c>
       <c r="E4" t="n">
-        <v>7.583333717179077</v>
+        <v>1.2322917290416</v>
       </c>
       <c r="F4" t="n">
-        <v>7.484792714670032</v>
+        <v>1.21627881613388</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.27529997040478</v>
+        <v>7.194736245190777</v>
       </c>
       <c r="D5" t="n">
-        <v>44.37220340215396</v>
+        <v>7.210483052850019</v>
       </c>
       <c r="E5" t="n">
-        <v>7.583333717179077</v>
+        <v>1.2322917290416</v>
       </c>
       <c r="F5" t="n">
-        <v>7.484792714670032</v>
+        <v>1.21627881613388</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
